--- a/sample/VTC Test Name List.xlsx
+++ b/sample/VTC Test Name List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cyrus\Desktop\Marking Sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E562D612-5D90-49A4-886C-44AE86DB8772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439DD5A4-6D1E-4CBF-863E-98CFD71197FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-705" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Name List" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Student</t>
-  </si>
-  <si>
     <t>Peter</t>
   </si>
   <si>
@@ -45,9 +39,6 @@
     <t>Susan</t>
   </si>
   <si>
-    <t>Class</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
@@ -58,6 +49,15 @@
   </si>
   <si>
     <t>D</t>
+  </si>
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>CLASS</t>
   </si>
 </sst>
 </file>
@@ -384,57 +384,57 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>123456789</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>987654321</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <v>234567890</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>345678912</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
